--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -713,7 +713,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>50</t>
@@ -731,7 +730,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>50</t>
@@ -749,7 +747,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -767,7 +764,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -785,7 +781,6 @@
           <t>WCSAXES</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>2</t>
@@ -803,7 +798,6 @@
           <t>CRPIX1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>33.0</t>
@@ -821,7 +815,6 @@
           <t>CRPIX2</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -839,7 +832,6 @@
           <t>PC1_1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -857,7 +849,6 @@
           <t>PC1_2</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>-0.92528941038182</t>
@@ -875,7 +866,6 @@
           <t>PC2_1</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>0.92528941038182</t>
@@ -893,7 +883,6 @@
           <t>PC2_2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -911,7 +900,6 @@
           <t>CDELT1</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -929,7 +917,6 @@
           <t>CDELT2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -947,7 +934,6 @@
           <t>CUNIT1</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>deg</t>
@@ -965,7 +951,6 @@
           <t>CUNIT2</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>deg</t>
@@ -983,7 +968,6 @@
           <t>CTYPE1</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>RA---TAN</t>
@@ -1001,7 +985,6 @@
           <t>CTYPE2</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>DEC--TAN</t>
@@ -1019,7 +1002,6 @@
           <t>CRVAL1</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>307.86215209961</t>
@@ -1037,7 +1019,6 @@
           <t>CRVAL2</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -1055,7 +1036,6 @@
           <t>LONPOLE</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>180.0</t>
@@ -1073,7 +1053,6 @@
           <t>LATPOLE</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -1091,7 +1070,6 @@
           <t>MJDREF</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1109,7 +1087,6 @@
           <t>RADESYS</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>ICRS</t>
@@ -1149,7 +1126,6 @@
           <t>IMSIZE0</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>50</t>
@@ -1167,7 +1143,6 @@
           <t>IMCRNR0</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>1001</t>
@@ -1185,7 +1160,6 @@
           <t>IMSIZE1</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>50</t>
@@ -1203,7 +1177,6 @@
           <t>IMCRNR1</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>995</t>
@@ -1221,7 +1194,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>O5aCQ5ZCO5aCO5WC</t>
@@ -1239,7 +1211,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>825708307</t>
@@ -1359,7 +1330,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>238</t>
@@ -1377,7 +1347,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1395,7 +1364,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -1413,13 +1381,11 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>ct / s</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1449,7 +1415,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>GlTbJjSbGjSbGjSb</t>
@@ -1467,7 +1432,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>2867743191</t>
@@ -1490,7 +1454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,7 +1561,6 @@
           <t>True</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1627,7 +1590,6 @@
           <t>NEXTEND</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>5</t>
@@ -1645,7 +1607,6 @@
           <t>SIMDATA</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1663,7 +1624,6 @@
           <t>SCIDATA</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>True</t>
@@ -1747,7 +1707,6 @@
           <t>CREATOR</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Pandora MOC</t>
@@ -1765,7 +1724,6 @@
           <t>CRSOFTV</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>v3.08</t>
@@ -1783,7 +1741,6 @@
           <t>COMPTYPE</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>1</t>
@@ -1801,7 +1758,6 @@
           <t>TRANSID</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>0</t>
@@ -1819,7 +1775,6 @@
           <t>FILENAME</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>/sssp/data/2026/08/15/2026-08-15__00-16-39_VisSci_KELT-9b_d050_n005_f11916_e000200000us.sp</t>
@@ -1837,7 +1792,6 @@
           <t>BITDEPTH</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>32</t>
@@ -1855,7 +1809,6 @@
           <t>TARG_ID</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>KELT-9b</t>
@@ -1873,7 +1826,6 @@
           <t>TARG_RA</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>307.8599548339844</t>
@@ -1891,7 +1843,6 @@
           <t>TARG_DEC</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>39.9389762878418</t>
@@ -1909,7 +1860,6 @@
           <t>FRMSREQD</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>12250</t>
@@ -1927,7 +1877,6 @@
           <t>FRMSCLCT</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>11916</t>
@@ -1945,7 +1894,6 @@
           <t>NUMSTARS</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>1</t>
@@ -1963,7 +1911,6 @@
           <t>STARDIMS</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>50</t>
@@ -1981,7 +1928,6 @@
           <t>NUMPCOAD</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>238</t>
@@ -1999,7 +1945,6 @@
           <t>FRMPCOAD</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>50</t>
@@ -2017,7 +1962,6 @@
           <t>ROISTRTX</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>995</t>
@@ -2035,7 +1979,6 @@
           <t>ROISTRTY</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>1001</t>
@@ -2053,7 +1996,6 @@
           <t>ROISIZEX</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>50</t>
@@ -2071,7 +2013,6 @@
           <t>ROISIZEY</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>50</t>
@@ -2089,7 +2030,6 @@
           <t>EXPTIME</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>200000</t>
@@ -2107,7 +2047,6 @@
           <t>RICEX</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>5</t>
@@ -2125,7 +2064,6 @@
           <t>RICEY</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>25</t>
@@ -2143,7 +2081,6 @@
           <t>CORRMODE</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>0</t>
@@ -2161,7 +2098,6 @@
           <t>CORSTIME</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>840068292</t>
@@ -2179,7 +2115,6 @@
           <t>FINETIME</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>8000000</t>
@@ -2197,7 +2132,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>6ddK9caI6caI6caI</t>
@@ -2215,7 +2149,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>0</t>
@@ -2233,13 +2166,11 @@
           <t>FIXED</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2247,13 +2178,11 @@
           <t>PFSOFTV</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>0.6.0</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2261,13 +2190,11 @@
           <t>PRSOFTV</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>2.9.1</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2275,13 +2202,11 @@
           <t>PFCLASS</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>VISDALevel2HDUList</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2289,7 +2214,6 @@
           <t>PFTIME</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>2026-09-09T19:39:22.758</t>
@@ -2307,7 +2231,6 @@
           <t>RA</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>307.86214468984406</t>
@@ -2325,7 +2248,6 @@
           <t>DEC</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>39.93879672813656</t>
@@ -2343,7 +2265,6 @@
           <t>ROLL</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>247.71571592394164</t>
@@ -2361,7 +2282,6 @@
           <t>POSX</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>1030.7329142663189</t>
@@ -2379,7 +2299,6 @@
           <t>POSY</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>1029.8410229048511</t>
@@ -2397,7 +2316,6 @@
           <t>GAIADR3</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>Gaia DR3 2064327278651198336</t>
@@ -2415,7 +2333,6 @@
           <t>GAIARA</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>307.8599027970418</t>
@@ -2433,7 +2350,6 @@
           <t>GAIADEC</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>39.93891900336815</t>
@@ -2451,7 +2367,6 @@
           <t>PARALLAX</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>4.825836101438949</t>
@@ -2469,7 +2384,6 @@
           <t>PMRA</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>16.716578051403854</t>
@@ -2487,7 +2401,6 @@
           <t>PMDEC</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>20.96090596020299</t>
@@ -2505,7 +2418,6 @@
           <t>2MASSID</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>2MASS J20312634+3956196</t>
@@ -2523,7 +2435,6 @@
           <t>J_M</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>7.458</t>
@@ -2541,7 +2452,6 @@
           <t>H_M</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>7.492</t>
@@ -2559,7 +2469,6 @@
           <t>K_M</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>7.482</t>
@@ -2577,7 +2486,6 @@
           <t>G_M</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>7.5902658552584015</t>
@@ -2595,7 +2503,6 @@
           <t>BP_M</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>7.594925828938212</t>
@@ -2613,7 +2520,6 @@
           <t>RP_M</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>7.552309075270038</t>
@@ -2631,7 +2537,6 @@
           <t>TEFF</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>9951.392</t>
@@ -2649,7 +2554,6 @@
           <t>LOGG</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>3.9497</t>
@@ -2667,7 +2571,6 @@
           <t>BKG10</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>40.870000000000005</t>
@@ -2685,7 +2588,6 @@
           <t>BKG50</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>219.5</t>
@@ -2703,7 +2605,6 @@
           <t>BKG90</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>318.6800000000001</t>
@@ -2721,7 +2622,6 @@
           <t>SRT_DATE</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>2026-08-15T00:17:35.008</t>
@@ -2739,7 +2639,6 @@
           <t>END_DATE</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>2026-08-15T00:57:15.008</t>
@@ -2757,7 +2656,6 @@
           <t>FILETIME</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>39.66666666666674</t>
@@ -2775,7 +2673,6 @@
           <t>VITLTIME</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>39.500000327825546</t>
@@ -2793,7 +2690,6 @@
           <t>ONTARG</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
           <t>100.0</t>
@@ -2811,7 +2707,6 @@
           <t>NKEEPOUT</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>47.89915966386555</t>
@@ -2829,7 +2724,6 @@
           <t>VKEEPOUT</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>21.84873949579832</t>
@@ -2847,7 +2741,6 @@
           <t>VITLMISS</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2865,7 +2758,6 @@
           <t>TARGTIME</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>False</t>
@@ -2883,7 +2775,6 @@
           <t>APCOMP1</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>100.0</t>
@@ -2898,66 +2789,70 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TARGCENT</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>TCENT10</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Target Centered</t>
+          <t>Fraction of time target within 10 px of center</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TARGCOMP</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>TCENT20</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Target Complete</t>
+          <t>Fraction of time target within 20 px of center</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>COMMENT</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>TCENT30</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Appended WCS.</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Fraction of time target within 30 px of center</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>COMMENT</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>TARGCOMP</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Appended WCS.</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Target Complete</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2965,13 +2860,11 @@
           <t>COMMENT</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2979,13 +2872,11 @@
           <t>COMMENT</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Appended Vectors.</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2993,13 +2884,35 @@
           <t>COMMENT</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
+          <t>Applied bias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Appended Vectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3109,13 +3022,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3123,13 +3034,11 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3137,13 +3046,11 @@
           <t>NAXIS3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3151,7 +3058,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3169,7 +3075,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
@@ -3209,7 +3114,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>RPDgTNAeRNAeRNAe</t>
@@ -3227,7 +3131,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>2307185145</t>
@@ -3245,13 +3148,11 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>ct / s</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3259,7 +3160,6 @@
           <t>WCSAXES</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>2</t>
@@ -3277,7 +3177,6 @@
           <t>CRPIX1</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>1028.0</t>
@@ -3295,7 +3194,6 @@
           <t>CRPIX2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>1024.0</t>
@@ -3313,7 +3211,6 @@
           <t>PC1_1</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -3331,7 +3228,6 @@
           <t>PC1_2</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>-0.92528941038182</t>
@@ -3349,7 +3245,6 @@
           <t>PC2_1</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>0.92528941038182</t>
@@ -3367,7 +3262,6 @@
           <t>PC2_2</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -3385,7 +3279,6 @@
           <t>CDELT1</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -3403,7 +3296,6 @@
           <t>CDELT2</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -3421,7 +3313,6 @@
           <t>CUNIT1</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>deg</t>
@@ -3439,7 +3330,6 @@
           <t>CUNIT2</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>deg</t>
@@ -3457,7 +3347,6 @@
           <t>CTYPE1</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>RA---TAN</t>
@@ -3475,7 +3364,6 @@
           <t>CTYPE2</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>DEC--TAN</t>
@@ -3493,7 +3381,6 @@
           <t>CRVAL1</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>307.86215209961</t>
@@ -3511,7 +3398,6 @@
           <t>CRVAL2</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -3529,7 +3415,6 @@
           <t>LONPOLE</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>180.0</t>
@@ -3547,7 +3432,6 @@
           <t>LATPOLE</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -3565,7 +3449,6 @@
           <t>MJDREF</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3583,7 +3466,6 @@
           <t>RADESYS</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>ICRS</t>
@@ -3601,7 +3483,6 @@
           <t>WCSAXES</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>2</t>
@@ -3619,7 +3500,6 @@
           <t>CRPIX1</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>1028.0</t>
@@ -3637,7 +3517,6 @@
           <t>CRPIX2</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>1024.0</t>
@@ -3655,7 +3534,6 @@
           <t>PC1_1</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -3673,7 +3551,6 @@
           <t>PC1_2</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>-0.92528941038182</t>
@@ -3691,7 +3568,6 @@
           <t>PC2_1</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>0.92528941038182</t>
@@ -3709,7 +3585,6 @@
           <t>PC2_2</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -3727,7 +3602,6 @@
           <t>CDELT1</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -3745,7 +3619,6 @@
           <t>CDELT2</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -3763,7 +3636,6 @@
           <t>CUNIT1</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>deg</t>
@@ -3781,7 +3653,6 @@
           <t>CUNIT2</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>deg</t>
@@ -3799,7 +3670,6 @@
           <t>CTYPE1</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>RA---TAN</t>
@@ -3817,7 +3687,6 @@
           <t>CTYPE2</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>DEC--TAN</t>
@@ -3835,7 +3704,6 @@
           <t>CRVAL1</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>307.86215209961</t>
@@ -3853,7 +3721,6 @@
           <t>CRVAL2</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -3871,7 +3738,6 @@
           <t>LONPOLE</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>180.0</t>
@@ -3889,7 +3755,6 @@
           <t>LATPOLE</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -3907,7 +3772,6 @@
           <t>MJDREF</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3925,7 +3789,6 @@
           <t>RADESYS</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>ICRS</t>
@@ -3943,7 +3806,6 @@
           <t>WCSAXES</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>2</t>
@@ -3961,7 +3823,6 @@
           <t>CRPIX1</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>1028.0</t>
@@ -3979,7 +3840,6 @@
           <t>CRPIX2</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>1024.0</t>
@@ -3997,7 +3857,6 @@
           <t>PC1_1</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -4015,7 +3874,6 @@
           <t>PC1_2</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>-0.92528941038182</t>
@@ -4033,7 +3891,6 @@
           <t>PC2_1</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>0.92528941038182</t>
@@ -4051,7 +3908,6 @@
           <t>PC2_2</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -4069,7 +3925,6 @@
           <t>CDELT1</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -4087,7 +3942,6 @@
           <t>CDELT2</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -4105,7 +3959,6 @@
           <t>CUNIT1</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>deg</t>
@@ -4123,7 +3976,6 @@
           <t>CUNIT2</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>deg</t>
@@ -4141,7 +3993,6 @@
           <t>CTYPE1</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>RA---TAN</t>
@@ -4159,7 +4010,6 @@
           <t>CTYPE2</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>DEC--TAN</t>
@@ -4177,7 +4027,6 @@
           <t>CRVAL1</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>307.86215209961</t>
@@ -4195,7 +4044,6 @@
           <t>CRVAL2</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -4213,7 +4061,6 @@
           <t>LONPOLE</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>180.0</t>
@@ -4231,7 +4078,6 @@
           <t>LATPOLE</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -4249,7 +4095,6 @@
           <t>MJDREF</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4267,7 +4112,6 @@
           <t>RADESYS</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>ICRS</t>
@@ -4387,13 +4231,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4401,7 +4243,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
@@ -4419,7 +4260,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -4437,7 +4277,6 @@
           <t>FRAME</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>JD</t>
@@ -4477,7 +4316,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>T7lpW7joT7joT7jo</t>
@@ -4495,7 +4333,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>1105499181</t>
@@ -4615,13 +4452,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4629,7 +4464,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
@@ -4647,7 +4481,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -4665,7 +4498,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>second</t>
@@ -4705,7 +4537,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>LmfaMjZSLjfYLjZY</t>
@@ -4723,7 +4554,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>2708996155</t>
@@ -4843,7 +4673,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>40</t>
@@ -4861,7 +4690,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>11915</t>
@@ -4879,7 +4707,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -4897,7 +4724,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -4947,7 +4773,6 @@
           <t>JD</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4965,7 +4790,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4983,7 +4807,6 @@
           <t>RightAscension</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5001,7 +4824,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5019,7 +4841,6 @@
           <t>Declination</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5037,7 +4858,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5055,7 +4875,6 @@
           <t>Rotation</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5073,7 +4892,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5091,7 +4909,6 @@
           <t>PCOTemp</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5109,7 +4926,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5127,7 +4943,6 @@
           <t>ASTROMETRY</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5157,7 +4972,6 @@
           <t>SDETMETH</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>1</t>
@@ -5175,7 +4989,6 @@
           <t>ATAITIME</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>840068292.008</t>
@@ -5193,7 +5006,6 @@
           <t>AIMMEAN</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>189.042358</t>
@@ -5211,7 +5023,6 @@
           <t>AIMSTD</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>19.295027</t>
@@ -5229,7 +5040,6 @@
           <t>ATHRESH1</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>67</t>
@@ -5247,7 +5057,6 @@
           <t>ATHRESH2</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>48</t>
@@ -5265,7 +5074,6 @@
           <t>AMINELLP</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5283,7 +5091,6 @@
           <t>AMAXELLP</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>0.85</t>
@@ -5301,7 +5108,6 @@
           <t>AMINFLUX</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>7</t>
@@ -5319,7 +5125,6 @@
           <t>AMAXFLUX</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>1600</t>
@@ -5337,7 +5142,6 @@
           <t>AXAXFLIP</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>1</t>
@@ -5355,7 +5159,6 @@
           <t>ASCAL</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>0.7899</t>
@@ -5373,7 +5176,6 @@
           <t>ASCALRMS</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>0.0004</t>
@@ -5391,7 +5193,6 @@
           <t>AROT</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>247.711</t>
@@ -5409,7 +5210,6 @@
           <t>AROTRMS</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>0.032</t>
@@ -5427,7 +5227,6 @@
           <t>ARA</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>307.860376</t>
@@ -5445,7 +5244,6 @@
           <t>ARARMS</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>8.489e-05</t>
@@ -5463,7 +5261,6 @@
           <t>ADEC</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>39.939956</t>
@@ -5481,7 +5278,6 @@
           <t>ADECRMS</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>6.817e-05</t>
@@ -5499,7 +5295,6 @@
           <t>AZERP</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>22.07</t>
@@ -5517,7 +5312,6 @@
           <t>AZERPRMS</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>0.16</t>
@@ -5535,7 +5329,6 @@
           <t>AQUADS</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>73</t>
@@ -5553,7 +5346,6 @@
           <t>AVERTS</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>102</t>
@@ -5571,7 +5363,6 @@
           <t>APHSTARS</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>24</t>
@@ -5589,7 +5380,6 @@
           <t>APOSTARS</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>24</t>
@@ -5607,7 +5397,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>5hXSAfVS8fVSAfVS</t>
@@ -5625,7 +5414,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>3204105511</t>
@@ -5745,7 +5533,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>130</t>
@@ -5763,7 +5550,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>238</t>
@@ -5781,7 +5567,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -5799,7 +5584,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -5849,7 +5633,6 @@
           <t>avg_ra</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5867,7 +5650,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5885,7 +5667,6 @@
           <t>avg_dec</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5903,7 +5684,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5921,7 +5701,6 @@
           <t>avg_rot</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5939,7 +5718,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5957,7 +5735,6 @@
           <t>err_ra</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5975,7 +5752,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5993,7 +5769,6 @@
           <t>err_dec</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6011,7 +5786,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6029,7 +5803,6 @@
           <t>err_rot</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6047,7 +5820,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6065,7 +5837,6 @@
           <t>jd</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6083,7 +5854,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6101,7 +5871,6 @@
           <t>exptime</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6119,7 +5888,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6137,7 +5905,6 @@
           <t>target_sep</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6155,7 +5922,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6173,7 +5939,6 @@
           <t>vitl_frames_count</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6191,7 +5956,6 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6209,7 +5973,6 @@
           <t>vitl_missing_frames</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6227,7 +5990,6 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6245,7 +6007,6 @@
           <t>earth_angle</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6263,7 +6024,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6281,7 +6041,6 @@
           <t>earth_illumination</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6299,7 +6058,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6317,7 +6075,6 @@
           <t>sun_angle</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6335,7 +6092,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6353,7 +6109,6 @@
           <t>visda_keepout</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6371,7 +6126,6 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6389,7 +6143,6 @@
           <t>nirda_keepout</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6407,7 +6160,6 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6425,7 +6177,6 @@
           <t>posx</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6443,7 +6194,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6461,7 +6211,6 @@
           <t>posy</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6479,7 +6228,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6497,7 +6245,6 @@
           <t>VECTORS</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6505,7 +6252,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>YAASa45RZAARa33R</t>
@@ -6523,7 +6269,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>1316492219</t>
@@ -6643,7 +6388,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>50</t>
@@ -6661,7 +6405,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>50</t>
@@ -6679,7 +6422,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -6697,7 +6439,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -6725,7 +6466,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6743,7 +6483,6 @@
           <t>32768</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6773,7 +6512,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>dA5ng93kdA3kd93k</t>
@@ -6791,7 +6529,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>43451034</t>
@@ -6911,7 +6648,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>50</t>
@@ -6929,7 +6665,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>50</t>
@@ -6947,7 +6682,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -6965,7 +6699,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -7005,7 +6738,6 @@
           <t>CONTAM</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7023,7 +6755,6 @@
           <t>COMPLTE</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>1.0017750354694497</t>
@@ -7041,7 +6772,6 @@
           <t>TOTAP</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>6064568.043967242</t>
@@ -7059,13 +6789,11 @@
           <t>RA</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>307.8599671153509</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7073,13 +6801,11 @@
           <t>DEC</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>39.93898083900071</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7087,13 +6813,11 @@
           <t>ROW</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>1029.7930278378888</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7101,13 +6825,11 @@
           <t>COLUMN</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>1030.7358547975248</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7115,13 +6837,11 @@
           <t>GAIA_ID</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>2064327278651198336</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7129,7 +6849,6 @@
           <t>IMSIZE0</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>50</t>
@@ -7147,7 +6866,6 @@
           <t>IMCRNR0</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>1001</t>
@@ -7165,7 +6883,6 @@
           <t>IMSIZE1</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>50</t>
@@ -7183,7 +6900,6 @@
           <t>IMCRNR1</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>995</t>
@@ -7201,7 +6917,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Fe3PIZ3MFd3MFZ3M</t>
@@ -7219,7 +6934,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>15335660</t>

--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -2850,7 +2850,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Target Complete</t>
+          <t>Over 70% of target aperture pixels usable</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -6551,7 +6551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6914,32 +6914,66 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>MAGSRC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fe3PIZ3MFd3MFZ3M</t>
+          <t>phot_bp_mean_mag</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-09T15:39:23</t>
+          <t>Catalog magnitude used for scene fluxes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>NOMAG</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Catalog stars without MAGSRC, given zero flux</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Fe3PIZ3MFd3MFZ3M</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-09-09T15:39:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>15335660</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>data unit checksum updated 2026-09-09T15:39:23</t>
         </is>

--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -4134,7 +4134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4313,32 +4313,49 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>TIMEPIXR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T7lpW7joT7joT7jo</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-09T15:39:23</t>
+          <t>TIME is the middle of each exposure</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>T7lpW7joT7joT7jo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-09-09T15:39:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>1105499181</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>data unit checksum updated 2026-09-09T15:39:23</t>
         </is>

--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -713,7 +713,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>50</t>
@@ -731,7 +730,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>50</t>
@@ -749,7 +747,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -767,7 +764,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -785,7 +781,6 @@
           <t>WCSAXES</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>2</t>
@@ -803,7 +798,6 @@
           <t>CRPIX1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>33.0</t>
@@ -821,7 +815,6 @@
           <t>CRPIX2</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -839,7 +832,6 @@
           <t>PC1_1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -857,7 +849,6 @@
           <t>PC1_2</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>-0.92528941038182</t>
@@ -875,7 +866,6 @@
           <t>PC2_1</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>0.92528941038182</t>
@@ -893,7 +883,6 @@
           <t>PC2_2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -911,7 +900,6 @@
           <t>CDELT1</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -929,7 +917,6 @@
           <t>CDELT2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -947,7 +934,6 @@
           <t>CUNIT1</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>deg</t>
@@ -965,7 +951,6 @@
           <t>CUNIT2</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>deg</t>
@@ -983,7 +968,6 @@
           <t>CTYPE1</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>RA---TAN</t>
@@ -1001,7 +985,6 @@
           <t>CTYPE2</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>DEC--TAN</t>
@@ -1019,7 +1002,6 @@
           <t>CRVAL1</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>307.86215209961</t>
@@ -1037,7 +1019,6 @@
           <t>CRVAL2</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -1055,7 +1036,6 @@
           <t>LONPOLE</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>180.0</t>
@@ -1073,7 +1053,6 @@
           <t>LATPOLE</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -1091,7 +1070,6 @@
           <t>MJDREF</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1109,7 +1087,6 @@
           <t>RADESYS</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>ICRS</t>
@@ -1149,7 +1126,6 @@
           <t>IMSIZE0</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>50</t>
@@ -1167,7 +1143,6 @@
           <t>IMCRNR0</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>1001</t>
@@ -1185,7 +1160,6 @@
           <t>IMSIZE1</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>50</t>
@@ -1203,7 +1177,6 @@
           <t>IMCRNR1</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>995</t>
@@ -1221,7 +1194,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>O5aCQ5ZCO5aCO5WC</t>
@@ -1239,7 +1211,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>825708307</t>
@@ -1359,7 +1330,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>238</t>
@@ -1377,7 +1347,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1395,7 +1364,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -1413,13 +1381,11 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>ct / s</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1449,7 +1415,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>GlTbJjSbGjSbGjSb</t>
@@ -1467,7 +1432,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>2867743191</t>
@@ -1490,7 +1454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,7 +1561,6 @@
           <t>True</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1627,7 +1590,6 @@
           <t>NEXTEND</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>5</t>
@@ -1645,7 +1607,6 @@
           <t>SIMDATA</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1663,7 +1624,6 @@
           <t>SCIDATA</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>True</t>
@@ -1747,7 +1707,6 @@
           <t>CREATOR</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Pandora MOC</t>
@@ -1765,7 +1724,6 @@
           <t>CRSOFTV</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>v3.08</t>
@@ -1783,7 +1741,6 @@
           <t>COMPTYPE</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>1</t>
@@ -1801,7 +1758,6 @@
           <t>TRANSID</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>0</t>
@@ -1819,7 +1775,6 @@
           <t>FILENAME</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>/sssp/data/2026/08/15/2026-08-15__00-16-39_VisSci_KELT-9b_d050_n005_f11916_e000200000us.sp</t>
@@ -1837,7 +1792,6 @@
           <t>BITDEPTH</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>32</t>
@@ -1855,7 +1809,6 @@
           <t>TARG_ID</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>KELT-9b</t>
@@ -1873,7 +1826,6 @@
           <t>TARG_RA</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>307.8599548339844</t>
@@ -1891,7 +1843,6 @@
           <t>TARG_DEC</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>39.9389762878418</t>
@@ -1909,7 +1860,6 @@
           <t>FRMSREQD</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>12250</t>
@@ -1927,7 +1877,6 @@
           <t>FRMSCLCT</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>11916</t>
@@ -1945,7 +1894,6 @@
           <t>NUMSTARS</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>1</t>
@@ -1963,7 +1911,6 @@
           <t>STARDIMS</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>50</t>
@@ -1981,7 +1928,6 @@
           <t>NUMPCOAD</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>238</t>
@@ -1999,7 +1945,6 @@
           <t>FRMPCOAD</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>50</t>
@@ -2017,7 +1962,6 @@
           <t>ROISTRTX</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>995</t>
@@ -2035,7 +1979,6 @@
           <t>ROISTRTY</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>1001</t>
@@ -2053,7 +1996,6 @@
           <t>ROISIZEX</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>50</t>
@@ -2071,7 +2013,6 @@
           <t>ROISIZEY</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>50</t>
@@ -2089,7 +2030,6 @@
           <t>EXPTIME</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>200000</t>
@@ -2107,7 +2047,6 @@
           <t>RICEX</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>5</t>
@@ -2125,7 +2064,6 @@
           <t>RICEY</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>25</t>
@@ -2143,7 +2081,6 @@
           <t>CORRMODE</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>0</t>
@@ -2161,7 +2098,6 @@
           <t>CORSTIME</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>840068292</t>
@@ -2179,7 +2115,6 @@
           <t>FINETIME</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>8000000</t>
@@ -2197,7 +2132,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>6ddK9caI6caI6caI</t>
@@ -2215,7 +2149,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>0</t>
@@ -2233,13 +2166,11 @@
           <t>FIXED</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2247,13 +2178,11 @@
           <t>PFSOFTV</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>0.6.0</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2261,13 +2190,11 @@
           <t>PRSOFTV</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>2.9.1</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2275,13 +2202,11 @@
           <t>PFCLASS</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>VISDALevel2HDUList</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2289,7 +2214,6 @@
           <t>PFTIME</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>2026-09-09T19:39:22.758</t>
@@ -2307,7 +2231,6 @@
           <t>RA</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>307.86214468984406</t>
@@ -2325,7 +2248,6 @@
           <t>DEC</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>39.93879672813656</t>
@@ -2343,7 +2265,6 @@
           <t>ROLL</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>247.71571592394164</t>
@@ -2361,7 +2282,6 @@
           <t>POSX</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>1030.7329142663189</t>
@@ -2379,7 +2299,6 @@
           <t>POSY</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>1029.8410229048511</t>
@@ -2397,7 +2316,6 @@
           <t>GAIADR3</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>Gaia DR3 2064327278651198336</t>
@@ -2415,7 +2333,6 @@
           <t>GAIARA</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>307.8599027970418</t>
@@ -2433,7 +2350,6 @@
           <t>GAIADEC</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>39.93891900336815</t>
@@ -2451,7 +2367,6 @@
           <t>PARALLAX</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>4.825836101438949</t>
@@ -2469,7 +2384,6 @@
           <t>PMRA</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>16.716578051403854</t>
@@ -2487,7 +2401,6 @@
           <t>PMDEC</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>20.96090596020299</t>
@@ -2505,7 +2418,6 @@
           <t>2MASSID</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>2MASS J20312634+3956196</t>
@@ -2523,7 +2435,6 @@
           <t>J_M</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>7.458</t>
@@ -2541,7 +2452,6 @@
           <t>H_M</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>7.492</t>
@@ -2559,7 +2469,6 @@
           <t>K_M</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>7.482</t>
@@ -2577,7 +2486,6 @@
           <t>G_M</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>7.5902658552584015</t>
@@ -2595,7 +2503,6 @@
           <t>BP_M</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>7.594925828938212</t>
@@ -2613,7 +2520,6 @@
           <t>RP_M</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>7.552309075270038</t>
@@ -2631,7 +2537,6 @@
           <t>TEFF</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>9951.392</t>
@@ -2649,7 +2554,6 @@
           <t>LOGG</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>3.9497</t>
@@ -2667,7 +2571,6 @@
           <t>BKG10</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>40.870000000000005</t>
@@ -2685,7 +2588,6 @@
           <t>BKG50</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>219.5</t>
@@ -2703,7 +2605,6 @@
           <t>BKG90</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>318.6800000000001</t>
@@ -2721,7 +2622,6 @@
           <t>SRT_DATE</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>2026-08-15T00:17:35.008</t>
@@ -2739,7 +2639,6 @@
           <t>END_DATE</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>2026-08-15T00:57:15.008</t>
@@ -2757,7 +2656,6 @@
           <t>FILETIME</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>39.66666666666674</t>
@@ -2775,7 +2673,6 @@
           <t>VITLTIME</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>39.500000327825546</t>
@@ -2793,7 +2690,6 @@
           <t>ONTARG</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
           <t>100.0</t>
@@ -2811,7 +2707,6 @@
           <t>NKEEPOUT</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>47.89915966386555</t>
@@ -2829,7 +2724,6 @@
           <t>VKEEPOUT</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>21.84873949579832</t>
@@ -2847,7 +2741,6 @@
           <t>VITLMISS</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2865,7 +2758,6 @@
           <t>TARGTIME</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>False</t>
@@ -2883,7 +2775,6 @@
           <t>APCOMP1</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>100.0</t>
@@ -2898,66 +2789,70 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TARGCENT</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>TCENT10</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Target Centered</t>
+          <t>Fraction of time target within 10 px of center</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TARGCOMP</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>TCENT20</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Target Complete</t>
+          <t>Fraction of time target within 20 px of center</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>COMMENT</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>TCENT30</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Appended WCS.</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Fraction of time target within 30 px of center</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>COMMENT</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>TARGCOMP</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Appended WCS.</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Over 70% of target aperture pixels usable</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2965,13 +2860,11 @@
           <t>COMMENT</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2979,13 +2872,11 @@
           <t>COMMENT</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Appended Vectors.</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2993,13 +2884,35 @@
           <t>COMMENT</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
+          <t>Applied bias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Appended Vectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3109,13 +3022,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3123,13 +3034,11 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3137,13 +3046,11 @@
           <t>NAXIS3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3151,7 +3058,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3169,7 +3075,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
@@ -3209,7 +3114,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>RPDgTNAeRNAeRNAe</t>
@@ -3227,7 +3131,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>2307185145</t>
@@ -3245,13 +3148,11 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>ct / s</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3259,7 +3160,6 @@
           <t>WCSAXES</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>2</t>
@@ -3277,7 +3177,6 @@
           <t>CRPIX1</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>1028.0</t>
@@ -3295,7 +3194,6 @@
           <t>CRPIX2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>1024.0</t>
@@ -3313,7 +3211,6 @@
           <t>PC1_1</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -3331,7 +3228,6 @@
           <t>PC1_2</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>-0.92528941038182</t>
@@ -3349,7 +3245,6 @@
           <t>PC2_1</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>0.92528941038182</t>
@@ -3367,7 +3262,6 @@
           <t>PC2_2</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -3385,7 +3279,6 @@
           <t>CDELT1</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -3403,7 +3296,6 @@
           <t>CDELT2</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -3421,7 +3313,6 @@
           <t>CUNIT1</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>deg</t>
@@ -3439,7 +3330,6 @@
           <t>CUNIT2</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>deg</t>
@@ -3457,7 +3347,6 @@
           <t>CTYPE1</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>RA---TAN</t>
@@ -3475,7 +3364,6 @@
           <t>CTYPE2</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>DEC--TAN</t>
@@ -3493,7 +3381,6 @@
           <t>CRVAL1</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>307.86215209961</t>
@@ -3511,7 +3398,6 @@
           <t>CRVAL2</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -3529,7 +3415,6 @@
           <t>LONPOLE</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>180.0</t>
@@ -3547,7 +3432,6 @@
           <t>LATPOLE</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -3565,7 +3449,6 @@
           <t>MJDREF</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3583,7 +3466,6 @@
           <t>RADESYS</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>ICRS</t>
@@ -3601,7 +3483,6 @@
           <t>WCSAXES</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>2</t>
@@ -3619,7 +3500,6 @@
           <t>CRPIX1</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>1028.0</t>
@@ -3637,7 +3517,6 @@
           <t>CRPIX2</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>1024.0</t>
@@ -3655,7 +3534,6 @@
           <t>PC1_1</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -3673,7 +3551,6 @@
           <t>PC1_2</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>-0.92528941038182</t>
@@ -3691,7 +3568,6 @@
           <t>PC2_1</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>0.92528941038182</t>
@@ -3709,7 +3585,6 @@
           <t>PC2_2</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -3727,7 +3602,6 @@
           <t>CDELT1</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -3745,7 +3619,6 @@
           <t>CDELT2</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -3763,7 +3636,6 @@
           <t>CUNIT1</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>deg</t>
@@ -3781,7 +3653,6 @@
           <t>CUNIT2</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>deg</t>
@@ -3799,7 +3670,6 @@
           <t>CTYPE1</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>RA---TAN</t>
@@ -3817,7 +3687,6 @@
           <t>CTYPE2</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>DEC--TAN</t>
@@ -3835,7 +3704,6 @@
           <t>CRVAL1</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>307.86215209961</t>
@@ -3853,7 +3721,6 @@
           <t>CRVAL2</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -3871,7 +3738,6 @@
           <t>LONPOLE</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>180.0</t>
@@ -3889,7 +3755,6 @@
           <t>LATPOLE</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -3907,7 +3772,6 @@
           <t>MJDREF</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3925,7 +3789,6 @@
           <t>RADESYS</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>ICRS</t>
@@ -3943,7 +3806,6 @@
           <t>WCSAXES</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>2</t>
@@ -3961,7 +3823,6 @@
           <t>CRPIX1</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>1028.0</t>
@@ -3979,7 +3840,6 @@
           <t>CRPIX2</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>1024.0</t>
@@ -3997,7 +3857,6 @@
           <t>PC1_1</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -4015,7 +3874,6 @@
           <t>PC1_2</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>-0.92528941038182</t>
@@ -4033,7 +3891,6 @@
           <t>PC2_1</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>0.92528941038182</t>
@@ -4051,7 +3908,6 @@
           <t>PC2_2</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>-0.37926179221649</t>
@@ -4069,7 +3925,6 @@
           <t>CDELT1</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -4087,7 +3942,6 @@
           <t>CDELT2</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>0.00021750277777778</t>
@@ -4105,7 +3959,6 @@
           <t>CUNIT1</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>deg</t>
@@ -4123,7 +3976,6 @@
           <t>CUNIT2</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>deg</t>
@@ -4141,7 +3993,6 @@
           <t>CTYPE1</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>RA---TAN</t>
@@ -4159,7 +4010,6 @@
           <t>CTYPE2</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>DEC--TAN</t>
@@ -4177,7 +4027,6 @@
           <t>CRVAL1</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>307.86215209961</t>
@@ -4195,7 +4044,6 @@
           <t>CRVAL2</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -4213,7 +4061,6 @@
           <t>LONPOLE</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>180.0</t>
@@ -4231,7 +4078,6 @@
           <t>LATPOLE</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>39.938789367676</t>
@@ -4249,7 +4095,6 @@
           <t>MJDREF</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4267,7 +4112,6 @@
           <t>RADESYS</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>ICRS</t>
@@ -4387,13 +4231,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4401,7 +4243,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
@@ -4419,7 +4260,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -4437,7 +4277,6 @@
           <t>FRAME</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>JD</t>
@@ -4477,7 +4316,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>T7lpW7joT7joT7jo</t>
@@ -4495,7 +4333,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>1105499181</t>
@@ -4615,13 +4452,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4629,7 +4464,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
@@ -4647,7 +4481,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -4665,7 +4498,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>second</t>
@@ -4705,7 +4537,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>LmfaMjZSLjfYLjZY</t>
@@ -4723,7 +4554,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>2708996155</t>
@@ -4843,7 +4673,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>40</t>
@@ -4861,7 +4690,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>11915</t>
@@ -4879,7 +4707,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -4897,7 +4724,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -4947,7 +4773,6 @@
           <t>JD</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4965,7 +4790,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4983,7 +4807,6 @@
           <t>RightAscension</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5001,7 +4824,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5019,7 +4841,6 @@
           <t>Declination</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5037,7 +4858,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5055,7 +4875,6 @@
           <t>Rotation</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5073,7 +4892,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5091,7 +4909,6 @@
           <t>PCOTemp</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5109,7 +4926,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5127,7 +4943,6 @@
           <t>ASTROMETRY</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5157,7 +4972,6 @@
           <t>SDETMETH</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>1</t>
@@ -5175,7 +4989,6 @@
           <t>ATAITIME</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>840068292.008</t>
@@ -5193,7 +5006,6 @@
           <t>AIMMEAN</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>189.042358</t>
@@ -5211,7 +5023,6 @@
           <t>AIMSTD</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>19.295027</t>
@@ -5229,7 +5040,6 @@
           <t>ATHRESH1</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>67</t>
@@ -5247,7 +5057,6 @@
           <t>ATHRESH2</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>48</t>
@@ -5265,7 +5074,6 @@
           <t>AMINELLP</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5283,7 +5091,6 @@
           <t>AMAXELLP</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>0.85</t>
@@ -5301,7 +5108,6 @@
           <t>AMINFLUX</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>7</t>
@@ -5319,7 +5125,6 @@
           <t>AMAXFLUX</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>1600</t>
@@ -5337,7 +5142,6 @@
           <t>AXAXFLIP</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>1</t>
@@ -5355,7 +5159,6 @@
           <t>ASCAL</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>0.7899</t>
@@ -5373,7 +5176,6 @@
           <t>ASCALRMS</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>0.0004</t>
@@ -5391,7 +5193,6 @@
           <t>AROT</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>247.711</t>
@@ -5409,7 +5210,6 @@
           <t>AROTRMS</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>0.032</t>
@@ -5427,7 +5227,6 @@
           <t>ARA</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>307.860376</t>
@@ -5445,7 +5244,6 @@
           <t>ARARMS</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>8.489e-05</t>
@@ -5463,7 +5261,6 @@
           <t>ADEC</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>39.939956</t>
@@ -5481,7 +5278,6 @@
           <t>ADECRMS</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>6.817e-05</t>
@@ -5499,7 +5295,6 @@
           <t>AZERP</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>22.07</t>
@@ -5517,7 +5312,6 @@
           <t>AZERPRMS</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>0.16</t>
@@ -5535,7 +5329,6 @@
           <t>AQUADS</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>73</t>
@@ -5553,7 +5346,6 @@
           <t>AVERTS</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>102</t>
@@ -5571,7 +5363,6 @@
           <t>APHSTARS</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>24</t>
@@ -5589,7 +5380,6 @@
           <t>APOSTARS</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>24</t>
@@ -5607,7 +5397,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>5hXSAfVS8fVSAfVS</t>
@@ -5625,7 +5414,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>3204105511</t>
@@ -5745,7 +5533,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>130</t>
@@ -5763,7 +5550,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>238</t>
@@ -5781,7 +5567,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -5799,7 +5584,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -5849,7 +5633,6 @@
           <t>avg_ra</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5867,7 +5650,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5885,7 +5667,6 @@
           <t>avg_dec</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5903,7 +5684,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5921,7 +5701,6 @@
           <t>avg_rot</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5939,7 +5718,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5957,7 +5735,6 @@
           <t>err_ra</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5975,7 +5752,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5993,7 +5769,6 @@
           <t>err_dec</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6011,7 +5786,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6029,7 +5803,6 @@
           <t>err_rot</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6047,7 +5820,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6065,7 +5837,6 @@
           <t>jd</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6083,7 +5854,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6101,7 +5871,6 @@
           <t>exptime</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6119,7 +5888,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6137,7 +5905,6 @@
           <t>target_sep</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6155,7 +5922,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6173,7 +5939,6 @@
           <t>vitl_frames_count</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6191,7 +5956,6 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6209,7 +5973,6 @@
           <t>vitl_missing_frames</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6227,7 +5990,6 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6245,7 +6007,6 @@
           <t>earth_angle</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6263,7 +6024,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6281,7 +6041,6 @@
           <t>earth_illumination</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6299,7 +6058,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6317,7 +6075,6 @@
           <t>sun_angle</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6335,7 +6092,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6353,7 +6109,6 @@
           <t>visda_keepout</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6371,7 +6126,6 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6389,7 +6143,6 @@
           <t>nirda_keepout</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6407,7 +6160,6 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6425,7 +6177,6 @@
           <t>posx</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6443,7 +6194,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6461,7 +6211,6 @@
           <t>posy</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6479,7 +6228,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6497,7 +6245,6 @@
           <t>VECTORS</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6505,7 +6252,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>YAASa45RZAARa33R</t>
@@ -6523,7 +6269,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>1316492219</t>
@@ -6643,7 +6388,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>50</t>
@@ -6661,7 +6405,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>50</t>
@@ -6679,7 +6422,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -6697,7 +6439,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -6725,7 +6466,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6743,7 +6483,6 @@
           <t>32768</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6773,7 +6512,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>dA5ng93kdA3kd93k</t>
@@ -6791,7 +6529,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>43451034</t>
@@ -6911,7 +6648,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>50</t>
@@ -6929,7 +6665,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>50</t>
@@ -6947,7 +6682,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -6965,7 +6699,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -7005,7 +6738,6 @@
           <t>CONTAM</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7023,7 +6755,6 @@
           <t>COMPLTE</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>1.0017750354694497</t>
@@ -7041,7 +6772,6 @@
           <t>TOTAP</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>6064568.043967242</t>
@@ -7059,13 +6789,11 @@
           <t>RA</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>307.8599671153509</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7073,13 +6801,11 @@
           <t>DEC</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>39.93898083900071</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7087,13 +6813,11 @@
           <t>ROW</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>1029.7930278378888</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7101,13 +6825,11 @@
           <t>COLUMN</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>1030.7358547975248</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7115,13 +6837,11 @@
           <t>GAIA_ID</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>2064327278651198336</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7129,7 +6849,6 @@
           <t>IMSIZE0</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>50</t>
@@ -7147,7 +6866,6 @@
           <t>IMCRNR0</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>1001</t>
@@ -7165,7 +6883,6 @@
           <t>IMSIZE1</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>50</t>
@@ -7183,7 +6900,6 @@
           <t>IMCRNR1</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>995</t>
@@ -7201,7 +6917,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Fe3PIZ3MFd3MFZ3M</t>
@@ -7219,7 +6934,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>15335660</t>

--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -4134,7 +4134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4341,6 +4341,28 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>data unit checksum updated 2026-09-09T15:39:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TIMESYS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Time scale</t>
         </is>
       </c>
     </row>
